--- a/public/templates/monthly-sales-template.xlsx
+++ b/public/templates/monthly-sales-template.xlsx
@@ -1,50 +1,163 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$Q$2</definedName>
   </definedNames>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="42">
+  <si>
+    <t>Store_ID</t>
+  </si>
+  <si>
+    <t>Store Name</t>
+  </si>
+  <si>
+    <t>Brand</t>
+  </si>
+  <si>
+    <t>Product Category</t>
+  </si>
+  <si>
+    <t>Device Sales</t>
+  </si>
+  <si>
+    <t>Plan Sales</t>
+  </si>
+  <si>
+    <t>Attach %</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>store_000001</t>
+  </si>
+  <si>
+    <t>Store_Name</t>
+  </si>
+  <si>
+    <t>Brand_name</t>
+  </si>
+  <si>
+    <t>Smartphone</t>
+  </si>
+  <si>
+    <t>store_000002</t>
+  </si>
+  <si>
+    <t>store_000003</t>
+  </si>
+  <si>
+    <t>store_000004</t>
+  </si>
+  <si>
+    <t>store_000005</t>
+  </si>
+  <si>
+    <t>store_000006</t>
+  </si>
+  <si>
+    <t>store_000007</t>
+  </si>
+  <si>
+    <t>store_000008</t>
+  </si>
+  <si>
+    <t>store_000009</t>
+  </si>
+  <si>
+    <t>store_000010</t>
+  </si>
+  <si>
+    <t>store_000011</t>
+  </si>
+  <si>
+    <t>store_000012</t>
+  </si>
+  <si>
+    <t>store_000013</t>
+  </si>
+  <si>
+    <t>store_000014</t>
+  </si>
+  <si>
+    <t>store_000015</t>
+  </si>
+  <si>
+    <t>store_000016</t>
+  </si>
+  <si>
+    <t>store_000017</t>
+  </si>
+  <si>
+    <t>store_000018</t>
+  </si>
+  <si>
+    <t>store_000019</t>
+  </si>
+  <si>
+    <t>store_000020</t>
+  </si>
+  <si>
+    <t>store_000021</t>
+  </si>
+  <si>
+    <t>store_000080</t>
+  </si>
+  <si>
+    <t>store_000081</t>
+  </si>
+  <si>
+    <t>store_000082</t>
+  </si>
+  <si>
+    <t>store_000083</t>
+  </si>
+  <si>
+    <t>store_000084</t>
+  </si>
+  <si>
+    <t>store_000085</t>
+  </si>
+  <si>
+    <t>store_000086</t>
+  </si>
+  <si>
+    <t>store_000087</t>
+  </si>
+  <si>
+    <t>store_000088</t>
+  </si>
+  <si>
+    <t>store_000089</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -67,14 +180,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="17" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -399,82 +523,96 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P33"/>
+  <sheetFormatPr customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Store_ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Store Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Brand</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Product Category</v>
-      </c>
-      <c r="E1">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1">
         <v>45870</v>
       </c>
-      <c r="I1">
+      <c r="F1"/>
+      <c r="G1"/>
+      <c r="H1"/>
+      <c r="I1" s="1">
         <v>45839</v>
       </c>
-      <c r="M1">
+      <c r="J1"/>
+      <c r="K1"/>
+      <c r="L1"/>
+      <c r="M1" s="1">
         <v>45809</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="E2" t="str">
-        <v>Device Sales</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Plan Sales</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Attach %</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Revenue</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Device Sales</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Plan Sales</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Attach %</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Revenue</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Device Sales</v>
-      </c>
-      <c r="N2" t="str">
-        <v>Plan Sales</v>
-      </c>
-      <c r="O2" t="str">
-        <v>Attach %</v>
-      </c>
-      <c r="P2" t="str">
-        <v>Revenue</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>store_000001</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Smartphone</v>
+      <c r="N1"/>
+      <c r="O1"/>
+      <c r="P1"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2"/>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" t="s">
+        <v>4</v>
+      </c>
+      <c r="N2" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" t="s">
+        <v>6</v>
+      </c>
+      <c r="P2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -513,18 +651,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>store_000002</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D4" t="str">
-        <v>Smartphone</v>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -563,18 +701,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>store_000003</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Smartphone</v>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -613,18 +751,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>store_000004</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Smartphone</v>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -663,18 +801,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>store_000005</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Smartphone</v>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -713,18 +851,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>store_000006</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Smartphone</v>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -763,18 +901,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>store_000007</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Smartphone</v>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -813,18 +951,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>store_000008</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Smartphone</v>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -863,18 +1001,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>store_000009</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Smartphone</v>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -913,18 +1051,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>store_000010</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D12" t="str">
-        <v>Smartphone</v>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -963,18 +1101,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>store_000011</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Smartphone</v>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1013,18 +1151,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>store_000012</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C14" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D14" t="str">
-        <v>Smartphone</v>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1063,18 +1201,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>store_000013</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Smartphone</v>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1113,18 +1251,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>store_000014</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Smartphone</v>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1163,18 +1301,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>store_000015</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Smartphone</v>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1213,18 +1351,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>store_000016</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D18" t="str">
-        <v>Smartphone</v>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1263,18 +1401,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>store_000017</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D19" t="str">
-        <v>Smartphone</v>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1313,18 +1451,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>store_000018</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D20" t="str">
-        <v>Smartphone</v>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1363,18 +1501,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>store_000019</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D21" t="str">
-        <v>Smartphone</v>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1413,18 +1551,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>store_000020</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Smartphone</v>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1463,18 +1601,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>store_000021</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C23" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D23" t="str">
-        <v>Smartphone</v>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1513,18 +1651,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>store_000080</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D24" t="str">
-        <v>Smartphone</v>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1563,18 +1701,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>store_000081</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C25" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Smartphone</v>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1613,18 +1751,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>store_000082</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D26" t="str">
-        <v>Smartphone</v>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1663,18 +1801,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>store_000083</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C27" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D27" t="str">
-        <v>Smartphone</v>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1713,18 +1851,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>store_000084</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C28" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D28" t="str">
-        <v>Smartphone</v>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1763,18 +1901,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>store_000085</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D29" t="str">
-        <v>Smartphone</v>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1813,18 +1951,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>store_000086</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D30" t="str">
-        <v>Smartphone</v>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1863,18 +2001,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>store_000087</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C31" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D31" t="str">
-        <v>Smartphone</v>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1913,18 +2051,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>store_000088</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C32" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D32" t="str">
-        <v>Smartphone</v>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1963,18 +2101,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>store_000089</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Store_Name</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Brand_name</v>
-      </c>
-      <c r="D33" t="str">
-        <v>Smartphone</v>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2015,17 +2153,14 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="M1:P1"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="E1:H1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P33"/>
-  </ignoredErrors>
 </worksheet>
 </file>